--- a/Base de Datos de Producción.xlsx
+++ b/Base de Datos de Producción.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://distrisodasa-my.sharepoint.com/personal/calcivar_grupofajardo_com_ec/Documents/Escritorio/Area Experimental/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="205" documentId="8_{B955A4F6-84E5-430B-B709-3831968721F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3EE8ADEC-9790-4650-8A8A-A257AFE6ED3B}"/>
+  <xr:revisionPtr revIDLastSave="263" documentId="8_{B955A4F6-84E5-430B-B709-3831968721F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B270D472-2B46-4C42-ADB1-E0DBEBDAB711}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{28CED21C-C055-4F6A-9369-9E65775F9B6E}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Produccion" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Produccion!$A$1:$AE$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Produccion!$A$1:$AE$67</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="47">
   <si>
     <t>AÑO</t>
   </si>
@@ -315,7 +315,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -364,6 +364,9 @@
     <xf numFmtId="4" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -699,7 +702,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB901F4C-F789-4902-887C-1D2717126825}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:AE61"/>
+  <dimension ref="A1:AE67"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="13" max="13" width="14.6640625" bestFit="1" customWidth="1"/>
@@ -808,7 +811,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5">
         <v>2026</v>
       </c>
@@ -1330,7 +1333,7 @@
       <c r="AD7" s="7"/>
       <c r="AE7" s="7"/>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
         <v>2026</v>
       </c>
@@ -1852,7 +1855,7 @@
       <c r="AD13" s="7"/>
       <c r="AE13" s="7"/>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5">
         <v>2026</v>
       </c>
@@ -2374,7 +2377,7 @@
       <c r="AD19" s="7"/>
       <c r="AE19" s="7"/>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5">
         <v>2026</v>
       </c>
@@ -2896,7 +2899,7 @@
       <c r="AD25" s="7"/>
       <c r="AE25" s="7"/>
     </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5">
         <v>2026</v>
       </c>
@@ -3418,7 +3421,7 @@
       <c r="AD31" s="8"/>
       <c r="AE31" s="8"/>
     </row>
-    <row r="32" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5">
         <v>2026</v>
       </c>
@@ -3940,7 +3943,7 @@
       <c r="AD37" s="7"/>
       <c r="AE37" s="7"/>
     </row>
-    <row r="38" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="9">
         <v>2026</v>
       </c>
@@ -4465,7 +4468,7 @@
       <c r="AD43" s="8"/>
       <c r="AE43" s="8"/>
     </row>
-    <row r="44" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="5">
         <v>2026</v>
       </c>
@@ -4990,7 +4993,7 @@
       <c r="AD49" s="8"/>
       <c r="AE49" s="8"/>
     </row>
-    <row r="50" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="9">
         <v>2026</v>
       </c>
@@ -5512,7 +5515,7 @@
       <c r="AD55" s="8"/>
       <c r="AE55" s="8"/>
     </row>
-    <row r="56" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:31" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="9">
         <v>2026</v>
       </c>
@@ -6045,11 +6048,547 @@
       <c r="AD61" s="8"/>
       <c r="AE61" s="8"/>
     </row>
+    <row r="62" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A62" s="9">
+        <v>2026</v>
+      </c>
+      <c r="B62" s="10">
+        <v>36</v>
+      </c>
+      <c r="C62" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D62" s="8">
+        <v>1</v>
+      </c>
+      <c r="E62" s="8">
+        <v>1</v>
+      </c>
+      <c r="F62" s="8">
+        <v>1</v>
+      </c>
+      <c r="G62" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="H62" s="8">
+        <v>1</v>
+      </c>
+      <c r="I62" s="8">
+        <v>0.09</v>
+      </c>
+      <c r="J62" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="K62" s="14">
+        <v>46191</v>
+      </c>
+      <c r="L62" s="15">
+        <v>46265</v>
+      </c>
+      <c r="M62" s="8">
+        <v>74</v>
+      </c>
+      <c r="N62" s="26">
+        <v>24.96</v>
+      </c>
+      <c r="O62" s="26">
+        <v>3.7</v>
+      </c>
+      <c r="P62" s="8">
+        <v>80</v>
+      </c>
+      <c r="Q62" s="8">
+        <v>80</v>
+      </c>
+      <c r="R62" s="8">
+        <v>80</v>
+      </c>
+      <c r="S62" s="18">
+        <v>22000</v>
+      </c>
+      <c r="T62" s="23">
+        <f>S62*N62/454</f>
+        <v>1209.5154185022027</v>
+      </c>
+      <c r="U62" s="18">
+        <f t="shared" ref="U62:U63" si="0">T62/0.09</f>
+        <v>13439.06020558003</v>
+      </c>
+      <c r="V62" s="18">
+        <v>1617.24</v>
+      </c>
+      <c r="W62" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="X62" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y62" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z62" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA62" s="7">
+        <v>1.35</v>
+      </c>
+      <c r="AB62" s="8"/>
+      <c r="AC62" s="8"/>
+      <c r="AD62" s="8"/>
+      <c r="AE62" s="8"/>
+    </row>
+    <row r="63" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A63" s="9">
+        <v>2026</v>
+      </c>
+      <c r="B63" s="10">
+        <v>36</v>
+      </c>
+      <c r="C63" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D63" s="8">
+        <v>2</v>
+      </c>
+      <c r="E63" s="8">
+        <v>1</v>
+      </c>
+      <c r="F63" s="8">
+        <v>1</v>
+      </c>
+      <c r="G63" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="H63" s="8">
+        <v>1</v>
+      </c>
+      <c r="I63" s="8">
+        <v>0.09</v>
+      </c>
+      <c r="J63" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="K63" s="14">
+        <v>46191</v>
+      </c>
+      <c r="L63" s="15">
+        <v>46265</v>
+      </c>
+      <c r="M63" s="8">
+        <v>74</v>
+      </c>
+      <c r="N63" s="26">
+        <v>23.46</v>
+      </c>
+      <c r="O63" s="26">
+        <v>2.4</v>
+      </c>
+      <c r="P63" s="8">
+        <v>80</v>
+      </c>
+      <c r="Q63" s="8">
+        <v>80</v>
+      </c>
+      <c r="R63" s="8">
+        <v>80</v>
+      </c>
+      <c r="S63" s="18">
+        <v>22000</v>
+      </c>
+      <c r="T63" s="23">
+        <v>1136.828</v>
+      </c>
+      <c r="U63" s="18">
+        <f t="shared" si="0"/>
+        <v>12631.422222222222</v>
+      </c>
+      <c r="V63" s="18">
+        <v>1616.81</v>
+      </c>
+      <c r="W63" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="X63" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y63" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z63" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA63" s="7">
+        <v>1.35</v>
+      </c>
+      <c r="AB63" s="8"/>
+      <c r="AC63" s="8"/>
+      <c r="AD63" s="8"/>
+      <c r="AE63" s="8"/>
+    </row>
+    <row r="64" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A64" s="9">
+        <v>2026</v>
+      </c>
+      <c r="B64" s="10">
+        <v>36</v>
+      </c>
+      <c r="C64" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D64" s="8">
+        <v>3</v>
+      </c>
+      <c r="E64" s="8">
+        <v>1</v>
+      </c>
+      <c r="F64" s="8">
+        <v>1</v>
+      </c>
+      <c r="G64" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="H64" s="8">
+        <v>1</v>
+      </c>
+      <c r="I64" s="8">
+        <v>0.09</v>
+      </c>
+      <c r="J64" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="K64" s="14">
+        <v>46191</v>
+      </c>
+      <c r="L64" s="15">
+        <v>46265</v>
+      </c>
+      <c r="M64" s="8">
+        <v>74</v>
+      </c>
+      <c r="N64" s="26">
+        <v>26.62</v>
+      </c>
+      <c r="O64" s="26">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="P64" s="8">
+        <v>80</v>
+      </c>
+      <c r="Q64" s="8">
+        <v>80</v>
+      </c>
+      <c r="R64" s="8">
+        <v>80</v>
+      </c>
+      <c r="S64" s="18">
+        <v>22000</v>
+      </c>
+      <c r="T64" s="23">
+        <v>1289.9558999999999</v>
+      </c>
+      <c r="U64" s="18">
+        <f>T64/0.09</f>
+        <v>14332.843333333332</v>
+      </c>
+      <c r="V64" s="18">
+        <f>U64/7</f>
+        <v>2047.5490476190475</v>
+      </c>
+      <c r="W64" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="X64" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y64" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z64" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA64" s="7">
+        <v>1.29</v>
+      </c>
+      <c r="AB64" s="8"/>
+      <c r="AC64" s="8"/>
+      <c r="AD64" s="8"/>
+      <c r="AE64" s="8"/>
+    </row>
+    <row r="65" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A65" s="9">
+        <v>2026</v>
+      </c>
+      <c r="B65" s="10">
+        <v>36</v>
+      </c>
+      <c r="C65" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D65" s="8">
+        <v>4</v>
+      </c>
+      <c r="E65" s="8">
+        <v>1</v>
+      </c>
+      <c r="F65" s="8">
+        <v>1</v>
+      </c>
+      <c r="G65" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="H65" s="8">
+        <v>1</v>
+      </c>
+      <c r="I65" s="8">
+        <v>0.09</v>
+      </c>
+      <c r="J65" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="K65" s="14">
+        <v>46191</v>
+      </c>
+      <c r="L65" s="15">
+        <v>46265</v>
+      </c>
+      <c r="M65" s="8">
+        <v>74</v>
+      </c>
+      <c r="N65" s="26">
+        <v>25.72</v>
+      </c>
+      <c r="O65" s="26">
+        <v>3.3</v>
+      </c>
+      <c r="P65" s="8">
+        <v>80</v>
+      </c>
+      <c r="Q65" s="8">
+        <v>80</v>
+      </c>
+      <c r="R65" s="8">
+        <v>80</v>
+      </c>
+      <c r="S65" s="18">
+        <v>22000</v>
+      </c>
+      <c r="T65" s="24">
+        <f>(S65*N65)/454</f>
+        <v>1246.3436123348017</v>
+      </c>
+      <c r="U65" s="18">
+        <f>T65/0.09</f>
+        <v>13848.262359275575</v>
+      </c>
+      <c r="V65" s="18">
+        <f>U65/7</f>
+        <v>1978.3231941822251</v>
+      </c>
+      <c r="W65" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="X65" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y65" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z65" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA65" s="8">
+        <v>1.27</v>
+      </c>
+      <c r="AB65" s="8"/>
+      <c r="AC65" s="8"/>
+      <c r="AD65" s="8"/>
+      <c r="AE65" s="8"/>
+    </row>
+    <row r="66" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A66" s="9">
+        <v>2026</v>
+      </c>
+      <c r="B66" s="10">
+        <v>36</v>
+      </c>
+      <c r="C66" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D66" s="8">
+        <v>5</v>
+      </c>
+      <c r="E66" s="8">
+        <v>1</v>
+      </c>
+      <c r="F66" s="8">
+        <v>1</v>
+      </c>
+      <c r="G66" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="H66" s="8">
+        <v>1</v>
+      </c>
+      <c r="I66" s="8">
+        <v>0.09</v>
+      </c>
+      <c r="J66" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="K66" s="14">
+        <v>46191</v>
+      </c>
+      <c r="L66" s="15">
+        <v>46265</v>
+      </c>
+      <c r="M66" s="8">
+        <v>74</v>
+      </c>
+      <c r="N66" s="26">
+        <v>26.51</v>
+      </c>
+      <c r="O66" s="26">
+        <v>2.4</v>
+      </c>
+      <c r="P66" s="8">
+        <v>80</v>
+      </c>
+      <c r="Q66" s="8">
+        <v>80</v>
+      </c>
+      <c r="R66" s="8">
+        <v>80</v>
+      </c>
+      <c r="S66" s="18">
+        <v>22000</v>
+      </c>
+      <c r="T66" s="24">
+        <f>S66*N66/454</f>
+        <v>1284.6255506607929</v>
+      </c>
+      <c r="U66" s="18">
+        <f>T66/0.09</f>
+        <v>14273.617229564366</v>
+      </c>
+      <c r="V66" s="18">
+        <f>U66/7</f>
+        <v>2039.0881756520523</v>
+      </c>
+      <c r="W66" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="X66" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y66" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z66" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA66" s="8">
+        <v>1.25</v>
+      </c>
+      <c r="AB66" s="8"/>
+      <c r="AC66" s="8"/>
+      <c r="AD66" s="8"/>
+      <c r="AE66" s="8"/>
+    </row>
+    <row r="67" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A67" s="9">
+        <v>2026</v>
+      </c>
+      <c r="B67" s="10">
+        <v>36</v>
+      </c>
+      <c r="C67" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D67" s="8">
+        <v>6</v>
+      </c>
+      <c r="E67" s="8">
+        <v>1</v>
+      </c>
+      <c r="F67" s="8">
+        <v>1</v>
+      </c>
+      <c r="G67" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="H67" s="8">
+        <v>1</v>
+      </c>
+      <c r="I67" s="8">
+        <v>0.09</v>
+      </c>
+      <c r="J67" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="K67" s="14">
+        <v>46191</v>
+      </c>
+      <c r="L67" s="15">
+        <v>46265</v>
+      </c>
+      <c r="M67" s="8">
+        <v>74</v>
+      </c>
+      <c r="N67" s="26">
+        <v>25.26</v>
+      </c>
+      <c r="O67" s="8">
+        <v>2.5</v>
+      </c>
+      <c r="P67" s="8">
+        <v>80</v>
+      </c>
+      <c r="Q67" s="8">
+        <v>80</v>
+      </c>
+      <c r="R67" s="8">
+        <v>80</v>
+      </c>
+      <c r="S67" s="18">
+        <v>22000</v>
+      </c>
+      <c r="T67" s="24">
+        <f>S67*N67/454</f>
+        <v>1224.0528634361233</v>
+      </c>
+      <c r="U67" s="18">
+        <f>T67/0.09</f>
+        <v>13600.587371512482</v>
+      </c>
+      <c r="V67" s="18">
+        <f>U67/7</f>
+        <v>1942.9410530732116</v>
+      </c>
+      <c r="W67" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="X67" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y67" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z67" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA67" s="8">
+        <v>1.26</v>
+      </c>
+      <c r="AB67" s="8"/>
+      <c r="AC67" s="8"/>
+      <c r="AD67" s="8"/>
+      <c r="AE67" s="8"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AE61" xr:uid="{FB901F4C-F789-4902-887C-1D2717126825}">
-    <filterColumn colId="2">
+  <autoFilter ref="A1:AE67" xr:uid="{FB901F4C-F789-4902-887C-1D2717126825}">
+    <filterColumn colId="1">
       <filters>
-        <filter val="LI001"/>
+        <filter val="36"/>
       </filters>
     </filterColumn>
   </autoFilter>
